--- a/01_Investment_Banking/_template_BASE.xlsx
+++ b/01_Investment_Banking/_template_BASE.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="120">
   <si>
     <t xml:space="preserve">[TICKER] — Company Name</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t xml:space="preserve">Total equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance check (Total assets - Total liabilities - Total equity, should = 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Cash Flow ($mm)</t>
@@ -556,116 +559,128 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -922,120 +937,120 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1059,270 +1074,270 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:H14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="C5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="C6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="C7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="s">
+      <c r="C8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="s">
+      <c r="C9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="10" t="s">
+      <c r="C10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="C11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10" t="s">
+      <c r="C12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="s">
+      <c r="C13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="10" t="s">
+      <c r="C14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1343,290 +1358,446 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:I20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14" t="n">
+        <f aca="false">E5*(1+Assumptions!C5)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <f aca="false">F5*(1+Assumptions!D5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <f aca="false">G5*(1+Assumptions!E5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <f aca="false">H5*(1+Assumptions!F5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14" t="str">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15" t="str">
         <f aca="false">IFERROR(D5/C5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="14" t="str">
+      <c r="E6" s="15" t="str">
         <f aca="false">IFERROR(E5/D5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="F6" s="14" t="str">
+      <c r="F6" s="15" t="str">
         <f aca="false">IFERROR(F5/E5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="G6" s="14" t="str">
+      <c r="G6" s="15" t="str">
         <f aca="false">IFERROR(G5/F5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="H6" s="14" t="str">
+      <c r="H6" s="15" t="str">
         <f aca="false">IFERROR(H5/G5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="I6" s="14" t="str">
+      <c r="I6" s="15" t="str">
         <f aca="false">IFERROR(I5/H5-1,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14" t="n">
+        <f aca="false">F5*(1-Assumptions!C6)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <f aca="false">G5*(1-Assumptions!D6)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <f aca="false">H5*(1-Assumptions!E6)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <f aca="false">I5*(1-Assumptions!F6)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13" t="n">
+      <c r="C8" s="14"/>
+      <c r="D8" s="14" t="n">
         <f aca="false">D5-D7</f>
         <v>0</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <f aca="false">E5-E7</f>
         <v>0</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <f aca="false">F5-F7</f>
         <v>0</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <f aca="false">G5-G7</f>
         <v>0</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="14" t="n">
         <f aca="false">H5-H7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="14" t="n">
         <f aca="false">I5-I7</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14" t="str">
+      <c r="C9" s="15"/>
+      <c r="D9" s="15" t="str">
         <f aca="false">IFERROR(D8/D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="E9" s="14" t="str">
+      <c r="E9" s="15" t="str">
         <f aca="false">IFERROR(E8/E5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F9" s="14" t="str">
+      <c r="F9" s="15" t="str">
         <f aca="false">IFERROR(F8/F5,"-")</f>
         <v>-</v>
       </c>
-      <c r="G9" s="14" t="str">
+      <c r="G9" s="15" t="str">
         <f aca="false">IFERROR(G8/G5,"-")</f>
         <v>-</v>
       </c>
-      <c r="H9" s="14" t="str">
+      <c r="H9" s="15" t="str">
         <f aca="false">IFERROR(H8/H5,"-")</f>
         <v>-</v>
       </c>
-      <c r="I9" s="14" t="str">
+      <c r="I9" s="15" t="str">
         <f aca="false">IFERROR(I8/I5,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14" t="n">
+        <f aca="false">F5*Assumptions!C7</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <f aca="false">G5*Assumptions!D7</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <f aca="false">H5*Assumptions!E7</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <f aca="false">I5*Assumptions!F7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14" t="n">
+        <f aca="false">F8-F10</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <f aca="false">G8-G10</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <f aca="false">H8-H10</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <f aca="false">I8-I10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15" t="str">
+        <f aca="false">IFERROR(F11/F5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G12" s="15" t="str">
+        <f aca="false">IFERROR(G11/G5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H12" s="15" t="str">
+        <f aca="false">IFERROR(H11/H5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I12" s="15" t="str">
+        <f aca="false">IFERROR(I11/I5,"-")</f>
+        <v>-</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14" t="n">
+        <f aca="false">F5*Assumptions!C10*Assumptions!C9</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <f aca="false">G5*Assumptions!D10*Assumptions!D9</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <f aca="false">H5*Assumptions!E10*Assumptions!E9</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <f aca="false">I5*Assumptions!F10*Assumptions!F9</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14" t="n">
+        <f aca="false">F11-F13</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <f aca="false">G11-G13</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <f aca="false">H11-H13</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <f aca="false">I11-I13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14" t="n">
+        <f aca="false">$E$15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <f aca="false">$E$15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <f aca="false">$E$15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <f aca="false">$E$15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14" t="n">
+        <f aca="false">F14-F15</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <f aca="false">G14-G15</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <f aca="false">H14-H15</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <f aca="false">I14-I15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14" t="n">
+        <f aca="false">F16*Assumptions!C8</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <f aca="false">G16*Assumptions!D8</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <f aca="false">H16*Assumptions!E8</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <f aca="false">I16*Assumptions!F8</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14" t="n">
+        <f aca="false">F16-F17</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <f aca="false">G16-G17</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <f aca="false">H16-H17</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <f aca="false">I16-I17</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14" t="n">
+        <f aca="false">Assumptions!C12</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <f aca="false">Assumptions!D12</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <f aca="false">Assumptions!E12</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <f aca="false">Assumptions!F12</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14" t="str">
+        <f aca="false">IFERROR(F18/F19,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G20" s="14" t="str">
+        <f aca="false">IFERROR(G18/G19,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H20" s="14" t="str">
+        <f aca="false">IFERROR(H18/H19,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I20" s="14" t="str">
+        <f aca="false">IFERROR(I18/I19,"-")</f>
+        <v>-</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1644,169 +1815,254 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:G17"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:G19"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="C8" s="14" t="n">
+        <f aca="false">C5+C6+C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <f aca="false">D5+D6+D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <f aca="false">E5+E6+E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <f aca="false">F5+F6+F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <f aca="false">G5+G6+G7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="C11" s="14" t="n">
+        <f aca="false">C8+C9+C10</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <f aca="false">D8+D9+D10</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <f aca="false">E8+E9+E10</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <f aca="false">F8+F9+F10</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <f aca="false">G8+G9+G10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="C14" s="14" t="n">
+        <f aca="false">C12+C13</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">D12+D13</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <f aca="false">E12+E13</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <f aca="false">F12+F13</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <f aca="false">G12+G13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
+      <c r="C16" s="14" t="n">
+        <f aca="false">C14+C15</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <f aca="false">D14+D15</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <f aca="false">E14+E15</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <f aca="false">F14+F15</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <f aca="false">G14+G15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <f aca="false">C11-C16-C17</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <f aca="false">D11-D16-D17</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <f aca="false">E11-E16-E17</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <f aca="false">F11-F16-F17</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <f aca="false">G11-G16-G17</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1825,128 +2081,191 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>75</v>
+      <c r="B2" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="19" t="n">
+        <f aca="false">IS!F18</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <f aca="false">IS!G18</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <f aca="false">IS!H18</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="B6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="19" t="n">
+        <f aca="false">IS!F13</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <f aca="false">IS!G13</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <f aca="false">IS!H13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="B8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <f aca="false">C5+C6+C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <f aca="false">D5+D6+D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <f aca="false">E5+E6+E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <f aca="false">F5+F6+F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <f aca="false">G5+G6+G7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="B9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
+      <c r="B10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <f aca="false">C8+C9</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <f aca="false">D8+D9</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <f aca="false">E8+E9</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <f aca="false">F8+F9</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <f aca="false">G8+G9</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="B11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="B12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="B13" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <f aca="false">C10+C11+C12</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">D10+D11+D12</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <f aca="false">E10+E11+E12</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <f aca="false">F10+F11+F12</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <f aca="false">G10+G11+G12</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1965,177 +2284,192 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>84</v>
+      <c r="B2" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="9" t="s">
         <v>86</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="15" t="s">
+      <c r="B5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="C5" s="20" t="n">
+        <f aca="false">IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <f aca="false">IS!G14*(1-Assumptions!D8)+IS!G13-IS!G5*Assumptions!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <f aca="false">IS!H14*(1-Assumptions!E8)+IS!H13-IS!H5*Assumptions!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <f aca="false">IS!I14*(1-Assumptions!F8)+IS!I13-IS!I5*Assumptions!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <f aca="false">F5*(1+Assumptions!G5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="18" t="n">
+      <c r="B6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(1)</f>
         <v>0.909090909090909</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(2)</f>
         <v>0.826446280991735</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(3)</f>
         <v>0.751314800901578</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(4)</f>
         <v>0.683013455365071</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(5)</f>
         <v>0.620921323059155</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="17" t="n">
+      <c r="H6" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="19" t="n">
+      <c r="B7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="23" t="n">
         <f aca="false">C5*C6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">D5*D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">E5*E6</f>
         <v>0</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">F5*F6</f>
         <v>0</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="23" t="n">
         <f aca="false">G5*G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="19" t="n">
+      <c r="H7" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="23" t="n">
         <f aca="false">G5*(1+I6)/(I5-I6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H8" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="19" t="n">
+      <c r="H8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="23" t="n">
         <f aca="false">I7*G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H9" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="19" t="n">
+      <c r="H9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="23" t="n">
         <f aca="false">SUM(C7:G7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H10" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" s="20" t="n">
+      <c r="H10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="24" t="n">
         <f aca="false">I8+I9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H11" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="21" t="n">
+      <c r="H11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H12" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="20" t="n">
+      <c r="H12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="24" t="n">
         <f aca="false">I10-I11</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H13" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="21" t="n">
+      <c r="H13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H14" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="20" t="n">
+      <c r="H14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="24" t="n">
         <f aca="false">I12/I13</f>
         <v>0</v>
       </c>
@@ -2157,228 +2491,228 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:H13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>100</v>
+      <c r="B2" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>107</v>
       </c>
+      <c r="H4" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="22" t="n">
+      <c r="B5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="22" t="n">
+      <c r="B6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="22" t="n">
+      <c r="B7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="22" t="n">
+      <c r="B8" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="22" t="n">
+      <c r="B9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22" t="n">
+      <c r="B10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="22" t="n">
+      <c r="B11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="20" t="n">
+      <c r="B13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="24" t="n">
         <f aca="false">MEDIAN(C5:C12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="24" t="n">
         <f aca="false">MEDIAN(D5:D12)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="24" t="n">
         <f aca="false">MEDIAN(E5:E12)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="27" t="n">
         <f aca="false">MEDIAN(F5:F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="27" t="n">
         <f aca="false">MEDIAN(G5:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="23" t="n">
+      <c r="H13" s="27" t="n">
         <f aca="false">MEDIAN(H5:H12)</f>
         <v>0</v>
       </c>
@@ -2400,136 +2734,136 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>110</v>
+      <c r="B2" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="25" t="n">
+      <c r="B4" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="29" t="n">
         <v>0.015</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="29" t="n">
         <v>0.025</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="29" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="25" t="n">
+      <c r="G4" s="29" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>112</v>
+      <c r="C5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="29" t="n">
         <v>0.09</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>112</v>
+      <c r="C6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>112</v>
+      <c r="C7" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="29" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>112</v>
+      <c r="C8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="29" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>112</v>
+      <c r="C9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2549,107 +2883,107 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>113</v>
+      <c r="B2" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>118</v>
       </c>
+      <c r="F4" s="9" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/01_Investment_Banking/_template_BASE.xlsx
+++ b/01_Investment_Banking/_template_BASE.xlsx
@@ -188,6 +188,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -204,7 +205,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -818,13 +818,13 @@
       <c r="E5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="23" t="n">
+      <c r="F5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,13 +843,13 @@
       <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="23" t="n">
+      <c r="F6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -868,13 +868,13 @@
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="23" t="n">
+      <c r="F7" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -893,13 +893,13 @@
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="23" t="n">
+      <c r="F8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,13 +918,13 @@
       <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="23" t="n">
+      <c r="F9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -943,13 +943,13 @@
       <c r="E10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="23" t="n">
+      <c r="F10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -968,13 +968,13 @@
       <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="23" t="n">
+      <c r="F11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -984,27 +984,27 @@
           <t>Median</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="22">
         <f>MEDIAN(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <f>MEDIAN(D5:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="22">
         <f>MEDIAN(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <f>MEDIAN(F5:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="25">
         <f>MEDIAN(G5:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="25">
         <f>MEDIAN(H5:H12)</f>
         <v/>
       </c>
@@ -1041,172 +1041,172 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>WACC \ Term. growth</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="27" t="n">
         <v>0.015</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="27" t="n">
         <v>0.02</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="27" t="n">
         <v>0.025</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="27" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="27" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="27" t="n">
         <v>0.08</v>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="27" t="n">
         <v>0.09</v>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="27" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="27" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="27" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
@@ -1270,74 +1270,74 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1395,10 +1395,10 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -1413,10 +1413,10 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="12" t="n">
         <v>200</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -1431,10 +1431,10 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="12" t="n">
         <v>100</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -1467,10 +1467,10 @@
           <t>Offer price</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="12" t="n">
         <v>9.5</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="12" t="n">
         <v>15</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -1521,10 +1521,10 @@
           <t>FCF Year 1</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="12" t="n">
         <v>70</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -1539,10 +1539,10 @@
           <t>FCF Year 2</t>
         </is>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="12" t="n">
         <v>65</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -1557,10 +1557,10 @@
           <t>FCF Year 3</t>
         </is>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="12" t="n">
         <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -1575,10 +1575,10 @@
           <t>FCF Year 4</t>
         </is>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="12" t="n">
         <v>55</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -1593,10 +1593,10 @@
           <t>FCF Year 5</t>
         </is>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="12" t="n">
         <v>50</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -1647,11 +1647,11 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="16">
         <f>C5-C6+C7</f>
         <v/>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="16">
         <f>D5-D6+D7</f>
         <v/>
       </c>
@@ -1662,11 +1662,11 @@
           <t>Bridge value / share</t>
         </is>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="16">
         <f>IFERROR(C21/C8,0)</f>
         <v/>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="16">
         <f>IFERROR(D21/D8,0)</f>
         <v/>
       </c>
@@ -1692,11 +1692,11 @@
           <t>PV of forecast FCF</t>
         </is>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="16">
         <f>C12/(1+C10)+C13/(1+C10)^2+C14/(1+C10)^3+C15/(1+C10)^4+C16/(1+C10)^5</f>
         <v/>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="16">
         <f>D12/(1+D10)+D13/(1+D10)^2+D14/(1+D10)^3+D15/(1+D10)^4+D16/(1+D10)^5</f>
         <v/>
       </c>
@@ -1707,11 +1707,11 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="16">
         <f>IF(C10&lt;=C11,"-",C16*(1+C11)/(C10-C11))</f>
         <v/>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="16">
         <f>IF(D10&lt;=D11,"-",D16*(1+D11)/(D10-D11))</f>
         <v/>
       </c>
@@ -1722,11 +1722,11 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="16">
         <f>IF(ISNUMBER(C25),C25/(1+C10)^5,"-")</f>
         <v/>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="16">
         <f>IF(ISNUMBER(D25),D25/(1+D10)^5,"-")</f>
         <v/>
       </c>
@@ -1737,11 +1737,11 @@
           <t>DCF enterprise value</t>
         </is>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="16">
         <f>IF(AND(ISNUMBER(C24),ISNUMBER(C26)),C24+C26,"-")</f>
         <v/>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="16">
         <f>IF(AND(ISNUMBER(D24),ISNUMBER(D26)),D24+D26,"-")</f>
         <v/>
       </c>
@@ -1752,11 +1752,11 @@
           <t>DCF equity value</t>
         </is>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="16">
         <f>IF(ISNUMBER(C27),C27-C6+C7,"-")</f>
         <v/>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="16">
         <f>IF(ISNUMBER(D27),D27-D6+D7,"-")</f>
         <v/>
       </c>
@@ -1767,11 +1767,11 @@
           <t>DCF value / share</t>
         </is>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="16">
         <f>IF(ISNUMBER(C28),C28/C8,"-")</f>
         <v/>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="16">
         <f>IF(ISNUMBER(D28),D28/D8,"-")</f>
         <v/>
       </c>
@@ -1792,7 +1792,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Terminal value is invalid whenever terminal growth is greater than or equal to the discount rate.</t>
         </is>
@@ -1854,10 +1854,10 @@
           <t>Buyer earnings</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="12" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1880,10 +1880,10 @@
           <t>Target earnings</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1893,10 +1893,10 @@
           <t>After-tax synergies</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1906,10 +1906,10 @@
           <t>Incremental financing cost</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="12" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1945,11 +1945,11 @@
           <t>Standalone EPS</t>
         </is>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="16">
         <f>IFERROR(C5/C6,0)</f>
         <v/>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="16">
         <f>IFERROR(D5/D6,0)</f>
         <v/>
       </c>
@@ -1960,11 +1960,11 @@
           <t>Pro forma earnings</t>
         </is>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="16">
         <f>C5+C7+C8-C9</f>
         <v/>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="16">
         <f>D5+D7+D8-D9</f>
         <v/>
       </c>
@@ -1975,11 +1975,11 @@
           <t>Pro forma shares</t>
         </is>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="16">
         <f>C6+C10</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="16">
         <f>D6+D10</f>
         <v/>
       </c>
@@ -1990,11 +1990,11 @@
           <t>Pro forma EPS</t>
         </is>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <f>IFERROR(C15/C16,0)</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <f>IFERROR(D15/D16,0)</f>
         <v/>
       </c>
@@ -2070,11 +2070,11 @@
           <t>Enterprise-to-equity bridge / share</t>
         </is>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <f>'Transaction Analysis'!C22</f>
         <v/>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <f>'Transaction Analysis'!D22</f>
         <v/>
       </c>
@@ -2090,11 +2090,11 @@
           <t>DCF value / share</t>
         </is>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <f>'Transaction Analysis'!C29</f>
         <v/>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <f>'Transaction Analysis'!D29</f>
         <v/>
       </c>
@@ -2110,11 +2110,11 @@
           <t>Offer price</t>
         </is>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="16">
         <f>'Transaction Analysis'!C9</f>
         <v/>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="16">
         <f>'Transaction Analysis'!D9</f>
         <v/>
       </c>
@@ -2204,7 +2204,7 @@
         <f>'Transaction Analysis'!C5-'Transaction Analysis'!C6+'Transaction Analysis'!C7-'Transaction Analysis'!C21</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>IF(ABS(C5)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -2224,7 +2224,7 @@
         <f>'Transaction Analysis'!C21-'Transaction Analysis'!C22*'Transaction Analysis'!C8</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>IF(ABS(C6)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -2244,7 +2244,7 @@
         <f>'Transaction Analysis'!D10-'Transaction Analysis'!D11</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>IF(C7&gt;0,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -2264,7 +2264,7 @@
         <f>'Transaction Analysis'!D23</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>IF(C8&lt;='Transaction Analysis'!D17,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -2284,7 +2284,7 @@
         <f>'Accretion Dilution'!D18</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>IF(C9&gt;='Accretion Dilution'!D11,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -2304,7 +2304,7 @@
         <f>'Transaction Analysis'!D30</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>IF(AND(ISNUMBER(C10),C10&lt;='Transaction Analysis'!D18),"PASS","BREACH")</f>
         <v/>
       </c>
@@ -4060,19 +4060,19 @@
       <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <f>E5*(1+Assumptions!C5)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <f>F5*(1+Assumptions!D5)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <f>G5*(1+Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <f>H5*(1+Assumptions!F5)</f>
         <v/>
       </c>
@@ -4083,28 +4083,28 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="14">
         <f>IFERROR(D5/C5-1,"-")</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>IFERROR(E5/D5-1,"-")</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>IFERROR(F5/E5-1,"-")</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>IFERROR(G5/F5-1,"-")</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>IFERROR(H5/G5-1,"-")</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>IFERROR(I5/H5-1,"-")</f>
         <v/>
       </c>
@@ -4118,19 +4118,19 @@
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>F5*(1-Assumptions!C6)</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>G5*(1-Assumptions!D6)</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <f>H5*(1-Assumptions!E6)</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <f>I5*(1-Assumptions!F6)</f>
         <v/>
       </c>
@@ -4142,27 +4142,27 @@
         </is>
       </c>
       <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5-D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5-E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5-F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5-G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>H5-H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <f>I5-I7</f>
         <v/>
       </c>
@@ -4173,28 +4173,28 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="14">
         <f>IFERROR(D8/D5,"-")</f>
         <v/>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <f>IFERROR(E8/E5,"-")</f>
         <v/>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>IFERROR(F8/F5,"-")</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>IFERROR(G8/G5,"-")</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f>IFERROR(H8/H5,"-")</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="14">
         <f>IFERROR(I8/I5,"-")</f>
         <v/>
       </c>
@@ -4208,19 +4208,19 @@
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F5*Assumptions!C7</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G5*Assumptions!D7</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <f>H5*Assumptions!E7</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <f>I5*Assumptions!F7</f>
         <v/>
       </c>
@@ -4234,19 +4234,19 @@
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>F8-F10</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>G8-G10</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <f>H8-H10</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <f>I8-I10</f>
         <v/>
       </c>
@@ -4257,22 +4257,22 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13">
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="14">
         <f>IFERROR(F11/F5,"-")</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>IFERROR(G11/G5,"-")</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <f>IFERROR(H11/H5,"-")</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="14">
         <f>IFERROR(I11/I5,"-")</f>
         <v/>
       </c>
@@ -4286,19 +4286,19 @@
       <c r="C13" s="12" t="n"/>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>F5*Assumptions!C10*Assumptions!C9</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>G5*Assumptions!D10*Assumptions!D9</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>H5*Assumptions!E10*Assumptions!E9</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <f>I5*Assumptions!F10*Assumptions!F9</f>
         <v/>
       </c>
@@ -4312,19 +4312,19 @@
       <c r="C14" s="12" t="n"/>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>F11-F13</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>G11-G13</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <f>H11-H13</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <f>I11-I13</f>
         <v/>
       </c>
@@ -4338,19 +4338,19 @@
       <c r="C15" s="12" t="n"/>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
@@ -4364,19 +4364,19 @@
       <c r="C16" s="12" t="n"/>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>F14-F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>G14-G15</f>
         <v/>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <f>H14-H15</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <f>I14-I15</f>
         <v/>
       </c>
@@ -4390,19 +4390,19 @@
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <f>F16*Assumptions!C8</f>
         <v/>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <f>G16*Assumptions!D8</f>
         <v/>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <f>H16*Assumptions!E8</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <f>I16*Assumptions!F8</f>
         <v/>
       </c>
@@ -4416,19 +4416,19 @@
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <f>F16-F17</f>
         <v/>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <f>G16-G17</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <f>H16-H17</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <f>I16-I17</f>
         <v/>
       </c>
@@ -4442,19 +4442,19 @@
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="12" t="n"/>
       <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <f>Assumptions!C12</f>
         <v/>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <f>Assumptions!D12</f>
         <v/>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <f>Assumptions!E12</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <f>Assumptions!F12</f>
         <v/>
       </c>
@@ -4468,19 +4468,19 @@
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <f>IFERROR(F18/F19,"-")</f>
         <v/>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <f>IFERROR(G18/G19,"-")</f>
         <v/>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <f>IFERROR(H18/H19,"-")</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <f>IFERROR(I18/I19,"-")</f>
         <v/>
       </c>
@@ -4554,11 +4554,11 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -4566,11 +4566,11 @@
           <t>Accounts receivable</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -4578,11 +4578,11 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -4590,23 +4590,23 @@
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -4617,11 +4617,11 @@
           <t>PP&amp;E net</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -4629,11 +4629,11 @@
           <t>Goodwill &amp; intangibles</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -4641,23 +4641,23 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <f>C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <f>D8+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>G8+G9+G10</f>
         <v/>
       </c>
@@ -4668,11 +4668,11 @@
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -4680,11 +4680,11 @@
           <t>Debt (current)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -4692,23 +4692,23 @@
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="13">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <f>E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>G12+G13</f>
         <v/>
       </c>
@@ -4719,11 +4719,11 @@
           <t>Long-term debt</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -4731,23 +4731,23 @@
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="13">
         <f>C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="13">
         <f>D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <f>E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>G14+G15</f>
         <v/>
       </c>
@@ -4758,35 +4758,35 @@
           <t>Total equity</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Balance check (Total assets - Total liabilities - Total equity, should = 0)</t>
         </is>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="16">
         <f>C11-C16-C17</f>
         <v/>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="16">
         <f>D11-D16-D17</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="16">
         <f>E11-E16-E17</f>
         <v/>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="16">
         <f>F11-F16-F17</f>
         <v/>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="16">
         <f>G11-G16-G17</f>
         <v/>
       </c>
@@ -4860,17 +4860,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="16">
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="17">
         <f>IS!F18</f>
         <v/>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="17">
         <f>IS!G18</f>
         <v/>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="17">
         <f>IS!H18</f>
         <v/>
       </c>
@@ -4881,17 +4881,17 @@
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="16">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="17">
         <f>IS!F13</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="17">
         <f>IS!G13</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="17">
         <f>IS!H13</f>
         <v/>
       </c>
@@ -4902,11 +4902,11 @@
           <t>+/- Change in NWC</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -4914,23 +4914,23 @@
           <t>Cash flow from operations</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -4941,11 +4941,11 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -4953,23 +4953,23 @@
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="13">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G8+G9</f>
         <v/>
       </c>
@@ -4980,11 +4980,11 @@
           <t>Debt issuance/(repayment)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -4992,11 +4992,11 @@
           <t>Dividends/buybacks</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -5004,23 +5004,23 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="13">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>G10+G11+G12</f>
         <v/>
       </c>
@@ -5036,7 +5036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I14"/>
+  <dimension ref="B2:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5096,23 +5096,23 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>IS!G14*(1-Assumptions!D8)+IS!G13-IS!G5*Assumptions!D10</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>IS!H14*(1-Assumptions!E8)+IS!H13-IS!H5*Assumptions!E10</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>IS!I14*(1-Assumptions!F8)+IS!I13-IS!I5*Assumptions!F10</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>F5*(1+Assumptions!G5)</f>
         <v/>
       </c>
@@ -5121,7 +5121,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5131,23 +5131,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <f>1/(1+$I$5)^(1)</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>1/(1+$I$5)^(2)</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>1/(1+$I$5)^(3)</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <f>1/(1+$I$5)^(4)</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <f>1/(1+$I$5)^(5)</f>
         <v/>
       </c>
@@ -5156,7 +5156,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="19" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -5166,23 +5166,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <f>F5*F6</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <f>G5*G6</f>
         <v/>
       </c>
@@ -5191,7 +5191,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="21">
         <f>G5*(1+I6)/(I5-I6)</f>
         <v/>
       </c>
@@ -5202,7 +5202,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="21">
         <f>I7*G6</f>
         <v/>
       </c>
@@ -5213,7 +5213,7 @@
           <t>Sum PV of FCF</t>
         </is>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="21">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
@@ -5224,7 +5224,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="22">
         <f>I8+I9</f>
         <v/>
       </c>
@@ -5235,7 +5235,7 @@
           <t>Less: net debt</t>
         </is>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="22">
         <f>I10-I11</f>
         <v/>
       </c>
@@ -5256,7 +5256,7 @@
           <t>Diluted shares (mm)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5266,8 +5266,19 @@
           <t>Implied value/share</t>
         </is>
       </c>
-      <c r="I14" s="21">
-        <f>I12/I13</f>
+      <c r="I14" s="22">
+        <f>IF(OR(IS!E5="",IS!E5=0),"n/a - no forecast base",I12/I13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Forecast base (IS!E5)</t>
+        </is>
+      </c>
+      <c r="I15" s="2">
+        <f>IF(OR(IS!E5="",IS!E5=0),"MISSING - the DCF cannot value anything","present")</f>
         <v/>
       </c>
     </row>
